--- a/naver-place-crawler/results_nail/천안_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/천안_네일샵.xlsx
@@ -421,8 +421,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -564,34 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>스튜디오 사일</t>
+          <t>졔졔네일</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>yujung0535@naver.com</t>
+          <t>es111222@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1402-6987</t>
+          <t>0507-1418-1353</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>충남 천안시 동남구 만남로 9 1층 120호 스튜디오사일</t>
+          <t>충남 천안시 동남구 먹거리9길 30-1 2층 zezenail</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_nail.sail_</t>
+          <t>http://instagram.com/zeze._nail</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,15 +601,19 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc02i5</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>131</v>
+        <v>602</v>
       </c>
       <c r="Q2" t="n">
-        <v>426</v>
+        <v>199</v>
       </c>
       <c r="R2" t="n">
-        <v>557</v>
+        <v>801</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2084883756</t>
+          <t>1974722599</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2084883756</t>
+          <t>https://m.place.naver.com/place/1974722599</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="Q3" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="R3" t="n">
-        <v>406</v>
+        <v>424</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -744,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -756,29 +760,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>네일뮤우</t>
+          <t>이구네일 불당점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>you_181@naver.com</t>
+          <t>eudemonic005@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0507-1401-0473</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>충남 천안시 동남구 충절로 30 1층 네일뮤우 NAIL MEW</t>
+          <t>충남 천안시 서북구 불당25로 8 나동 131호 이구네일</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://place.map.kakao.com/1349616484#home</t>
+          <t>http://pf.kakao.com/_xlxgxois/83330073</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -798,32 +798,28 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wlo7qj3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>308</v>
+        <v>5820</v>
       </c>
       <c r="Q4" t="n">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="R4" t="n">
-        <v>390</v>
+        <v>5859</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,17 +828,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2085422518</t>
+          <t>1108135278</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2085422518</t>
+          <t>https://m.place.naver.com/place/1108135278</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -854,29 +850,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>다이아네일링 천안두정점</t>
+          <t>오늘지나네일</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>rhdwn135135@naver.com</t>
+          <t>zpzp9285@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0507-1442-6568</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 원두정10길 28 2층 다이아네일링</t>
+          <t>충남 천안시 서북구 불당24로 9 불당LH 1단지, 단지내상가 오늘지나네일</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rhdwn135135</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -886,24 +878,20 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4kgvx</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -911,17 +899,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>400</v>
+        <v>6905</v>
       </c>
       <c r="Q5" t="n">
-        <v>239</v>
+        <v>26</v>
       </c>
       <c r="R5" t="n">
-        <v>639</v>
+        <v>6931</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1119429423</t>
+          <t>1817373039</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1119429423</t>
+          <t>https://m.place.naver.com/place/1817373039</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -952,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>시에뷰티네일</t>
+          <t>스튜디오 사일</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>tjsdud8676@naver.com</t>
+          <t>yujung0535@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1354-4713</t>
+          <t>0507-1402-6987</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 미라8길 33 3층 303호</t>
+          <t>충남 천안시 동남구 만남로 9 1층 120호 스튜디오사일</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://youtube.com/@syebeautynail?si=QFJXPaH7QnSiQTS-</t>
+          <t>https://www.instagram.com/_nail.sail_</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -994,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5tkb9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1013,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>345</v>
+        <v>137</v>
       </c>
       <c r="Q6" t="n">
-        <v>630</v>
+        <v>426</v>
       </c>
       <c r="R6" t="n">
-        <v>975</v>
+        <v>563</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1942226175</t>
+          <t>2084883756</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1942226175</t>
+          <t>https://m.place.naver.com/place/2084883756</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1070,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1115,13 +1099,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3073</v>
+        <v>3097</v>
       </c>
       <c r="Q7" t="n">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="R7" t="n">
-        <v>3660</v>
+        <v>3683</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1140,7 +1124,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1213,13 +1197,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1109</v>
+        <v>1129</v>
       </c>
       <c r="Q8" t="n">
         <v>88</v>
       </c>
       <c r="R8" t="n">
-        <v>1197</v>
+        <v>1217</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1238,7 +1222,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1234,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>네일한누리</t>
+          <t>네일라비아</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>princess5648@naver.com</t>
+          <t>sun_jeong2@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1348-7712</t>
+          <t>0507-1459-2062</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>충남 천안시 동남구 서부대로 252 상가동 2층 203호</t>
+          <t>충남 천안시 서북구 두정중10길 2 타워오피스텔 1층 네일라비아</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail._.han_nury?igsh=MTU5aW1kMnFlZTd2dg==</t>
+          <t>https://www.instagram.com/nail_rabia__</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1297,12 +1281,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wzcv22w</t>
+          <t>https://talk.naver.com/ct/w46h39</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1311,13 +1295,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>306</v>
+        <v>358</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="R9" t="n">
-        <v>310</v>
+        <v>384</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,17 +1310,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1718734202</t>
+          <t>1958470967</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1718734202</t>
+          <t>https://m.place.naver.com/place/1958470967</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1348,29 +1332,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>네일미뮤</t>
+          <t>네일한누리</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>yoonhye_1004@naver.com</t>
+          <t>princess5648@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1434-0842</t>
+          <t>0507-1348-7712</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충남 천안시 동남구 먹거리1길 1 1층</t>
+          <t>충남 천안시 동남구 서부대로 252 상가동 2층 203호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailmimew/</t>
+          <t>https://www.instagram.com/nail._.han_nury?igsh=MTU5aW1kMnFlZTd2dg==</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1395,12 +1379,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wayrhnt</t>
+          <t>https://talk.naver.com/ct/wzcv22w</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1409,13 +1393,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>669</v>
+        <v>313</v>
       </c>
       <c r="Q10" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>687</v>
+        <v>317</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,17 +1408,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1128614095</t>
+          <t>1718734202</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1128614095</t>
+          <t>https://m.place.naver.com/place/1718734202</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1446,29 +1430,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>그리미네일 두정점</t>
+          <t>레푸스 천안두정점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>hewxn31z@naver.com</t>
+          <t>refusscheonan@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1413-3985</t>
+          <t>0507-1440-0145</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 두정고6길 29 1층</t>
+          <t>충남 천안시 서북구 두정로 177 고바우빌딩 2F</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/grimmy.nail</t>
+          <t>https://blog.naver.com/refusscheonan</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1483,7 +1467,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1493,12 +1477,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ydacp</t>
+          <t>https://talk.naver.com/ct/w5t6e6</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1507,13 +1491,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>128</v>
+        <v>2282</v>
       </c>
       <c r="Q11" t="n">
-        <v>170</v>
+        <v>548</v>
       </c>
       <c r="R11" t="n">
-        <v>298</v>
+        <v>2830</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,17 +1506,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2060892584</t>
+          <t>20103899</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2060892584</t>
+          <t>https://m.place.naver.com/place/20103899</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/천안_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/천안_네일샵.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="49" customWidth="1" min="7" max="7"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="Q2" t="n">
         <v>199</v>
       </c>
       <c r="R2" t="n">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -662,29 +662,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>푸르민네일</t>
+          <t>이구네일 불당점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>iyumin0629@naver.com</t>
+          <t>eudemonic005@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0507-1363-9659</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 불당25로 8 호반써밋플레이스아파트 상가 B동 146호 푸르민네일</t>
+          <t>충남 천안시 서북구 불당25로 8 나동 131호 이구네일</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://sites.google.com/view/minnailpureu/%ED%99%88</t>
+          <t>http://pf.kakao.com/_xlxgxois/83330073</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,37 +695,33 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w49i3b</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>304</v>
+        <v>5829</v>
       </c>
       <c r="Q3" t="n">
-        <v>120</v>
+        <v>39</v>
       </c>
       <c r="R3" t="n">
-        <v>424</v>
+        <v>5868</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1454394628</t>
+          <t>1108135278</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1454394628</t>
+          <t>https://m.place.naver.com/place/1108135278</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -760,12 +752,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>이구네일 불당점</t>
+          <t>오늘지나네일</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>eudemonic005@naver.com</t>
+          <t>zpzp9285@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -773,22 +765,22 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 불당25로 8 나동 131호 이구네일</t>
+          <t>충남 천안시 서북구 불당24로 9 불당LH 1단지, 단지내상가 오늘지나네일</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xlxgxois/83330073</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -804,7 +796,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -813,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>5820</v>
+        <v>6934</v>
       </c>
       <c r="Q4" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="R4" t="n">
-        <v>5859</v>
+        <v>6960</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,17 +820,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1108135278</t>
+          <t>1817373039</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1108135278</t>
+          <t>https://m.place.naver.com/place/1817373039</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -850,7 +842,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>오늘지나네일</t>
+          <t>이구네일 백석점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -863,12 +855,12 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 불당24로 9 불당LH 1단지, 단지내상가 오늘지나네일</t>
+          <t>충남 천안시 서북구 한들3로 51 1층 101호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/29nailro10</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,7 +870,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -899,17 +891,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>6905</v>
+        <v>2340</v>
       </c>
       <c r="Q5" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="R5" t="n">
-        <v>6931</v>
+        <v>2356</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +910,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1817373039</t>
+          <t>1041668384</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1817373039</t>
+          <t>https://m.place.naver.com/place/1041668384</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -940,39 +932,43 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>스튜디오 사일</t>
+          <t>레푸스 천안쌍용점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>yujung0535@naver.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>eopls@naver.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>cto@handsos.com</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1402-6987</t>
+          <t>041-556-2440</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>충남 천안시 동남구 만남로 9 1층 120호 스튜디오사일</t>
+          <t>충남 천안시 서북구 쌍용대로 137 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_nail.sail_</t>
+          <t>https://booking.naver.com/booking/13/bizes/778197</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -982,10 +978,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w49yg3</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>137</v>
+        <v>3112</v>
       </c>
       <c r="Q6" t="n">
-        <v>426</v>
+        <v>589</v>
       </c>
       <c r="R6" t="n">
-        <v>563</v>
+        <v>3701</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2084883756</t>
+          <t>36293176</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2084883756</t>
+          <t>https://m.place.naver.com/place/36293176</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1034,38 +1034,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>레푸스 천안쌍용점</t>
+          <t>이엘네일</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>eopls@naver.com</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>cto@handsos.com</t>
-        </is>
-      </c>
+          <t>elwaxing@naver.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>041-556-2440</t>
+          <t>0507-1412-2451</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 쌍용대로 137 2층</t>
+          <t>충남 천안시 서북구 불당31길 26 지혜성빌 101호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/13/bizes/778197</t>
+          <t>http://www.instagram.com/ellash_nail</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1085,7 +1081,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w49yg3</t>
+          <t>https://talk.naver.com/ct/wc53pk</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1099,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3097</v>
+        <v>1137</v>
       </c>
       <c r="Q7" t="n">
-        <v>586</v>
+        <v>88</v>
       </c>
       <c r="R7" t="n">
-        <v>3683</v>
+        <v>1225</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1114,17 +1110,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>36293176</t>
+          <t>1713959834</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36293176</t>
+          <t>https://m.place.naver.com/place/1713959834</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1136,29 +1132,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>이엘네일</t>
+          <t>네일라비아</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>elwaxing@naver.com</t>
+          <t>sun_jeong2@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1412-2451</t>
+          <t>0507-1459-2062</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 불당31길 26 지혜성빌 101호</t>
+          <t>충남 천안시 서북구 두정중10길 2 타워오피스텔 1층 네일라비아</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/ellash_nail</t>
+          <t>https://www.instagram.com/nail_rabia__</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1183,7 +1179,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc53pk</t>
+          <t>https://talk.naver.com/ct/w46h39</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1197,13 +1193,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1129</v>
+        <v>359</v>
       </c>
       <c r="Q8" t="n">
-        <v>88</v>
+        <v>26</v>
       </c>
       <c r="R8" t="n">
-        <v>1217</v>
+        <v>385</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1212,17 +1208,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1713959834</t>
+          <t>1958470967</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1713959834</t>
+          <t>https://m.place.naver.com/place/1958470967</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1234,29 +1230,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>네일라비아</t>
+          <t>네일한누리</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sun_jeong2@naver.com</t>
+          <t>princess5648@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1459-2062</t>
+          <t>0507-1348-7712</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 두정중10길 2 타워오피스텔 1층 네일라비아</t>
+          <t>충남 천안시 동남구 서부대로 252 상가동 2층 203호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_rabia__</t>
+          <t>https://www.instagram.com/nail._.han_nury?igsh=MTU5aW1kMnFlZTd2dg==</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1281,12 +1277,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w46h39</t>
+          <t>https://talk.naver.com/ct/wzcv22w</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1295,13 +1291,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>358</v>
+        <v>314</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>384</v>
+        <v>318</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1310,17 +1306,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1958470967</t>
+          <t>1718734202</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1958470967</t>
+          <t>https://m.place.naver.com/place/1718734202</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1332,29 +1328,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>네일한누리</t>
+          <t>네일하우스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>princess5648@naver.com</t>
+          <t>toy_21c@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1348-7712</t>
+          <t>0507-1356-3410</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충남 천안시 동남구 서부대로 252 상가동 2층 203호</t>
+          <t>충남 천안시 서북구 두정중9길 1-4 1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail._.han_nury?igsh=MTU5aW1kMnFlZTd2dg==</t>
+          <t>https://www.instagram.com/tjsl_1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1379,12 +1375,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wzcv22w</t>
+          <t>https://talk.naver.com/ct/wlbvzh7</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1393,13 +1389,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>313</v>
+        <v>47</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="R10" t="n">
-        <v>317</v>
+        <v>81</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1408,17 +1404,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1718734202</t>
+          <t>1578775754</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1718734202</t>
+          <t>https://m.place.naver.com/place/1578775754</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1430,29 +1426,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>레푸스 천안두정점</t>
+          <t>네일리현</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>refusscheonan@naver.com</t>
+          <t>nail_leehyeon@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1440-0145</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 두정로 177 고바우빌딩 2F</t>
+          <t>충남 천안시 서북구 봉정로 324 A동 106호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/refusscheonan</t>
+          <t>https://blog.naver.com/nail_leehyeon</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1477,12 +1469,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5t6e6</t>
+          <t>https://talk.naver.com/ct/w7tw7ln</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1491,13 +1483,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2282</v>
+        <v>73</v>
       </c>
       <c r="Q11" t="n">
-        <v>548</v>
+        <v>23</v>
       </c>
       <c r="R11" t="n">
-        <v>2830</v>
+        <v>96</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1506,17 +1498,589 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>20103899</t>
+          <t>2092215826</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20103899</t>
+          <t>https://m.place.naver.com/place/2092215826</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>네일드이브</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ggomji_rak@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1321-0649</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>충남 천안시 서북구 불당26로 144 근린생활시설3동 지1층 3-103호</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_wKKgn</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wm8m34d</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>114</v>
+      </c>
+      <c r="R12" t="n">
+        <v>155</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2012576649</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2012576649</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>네일레이어</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>naillayer-@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1362-6230</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>충남 천안시 서북구 두정로 236 스타펠리스218호</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/naillayer-</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3</v>
+      </c>
+      <c r="R13" t="n">
+        <v>43</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2044059918</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2044059918</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>멜루네일</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ssunii76_@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1312-4412</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>충남 천안시 서북구 서부11길 50 블루빌 1층 101호</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/melu_nail_</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wzwjq2c</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>29</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2054396755</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2054396755</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>네일이로에</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>aeunzxn@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>충남 천안시 동남구 충절로 79 1층</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_iroe</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3</v>
+      </c>
+      <c r="R15" t="n">
+        <v>49</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2016538852</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2016538852</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>브리네일</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>jv1110@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1306-1557</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>충남 천안시 서북구 월봉4로 84-5 D동 101호</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/brie_nail?igsh=YzNnaDB2MGhlaXo5&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wfwafxh</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>19</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>2047884394</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2047884394</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>네오뷰티네일</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>sum_mer_lov_e@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1393-1054</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>충남 천안시 동남구 통정10로 69-7 2층 202호</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/neo_beauty_sunny?igsh=MThkOTR2cHJoczhhNw==</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>15</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2080241609</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2080241609</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/천안_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/천안_네일샵.xlsx
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="Q2" t="n">
         <v>199</v>
       </c>
       <c r="R2" t="n">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -662,12 +662,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>이구네일 불당점</t>
+          <t>이구네일 백석점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>eudemonic005@naver.com</t>
+          <t>zpzp9285@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -675,17 +675,17 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 불당25로 8 나동 131호 이구네일</t>
+          <t>충남 천안시 서북구 한들3로 51 1층 101호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xlxgxois/83330073</t>
+          <t>https://www.instagram.com/29nailro10</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -706,22 +706,22 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>5829</v>
+        <v>2341</v>
       </c>
       <c r="Q3" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="R3" t="n">
-        <v>5868</v>
+        <v>2357</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1108135278</t>
+          <t>1041668384</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1108135278</t>
+          <t>https://m.place.naver.com/place/1041668384</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>오늘지나네일</t>
+          <t>이구네일 불당점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>zpzp9285@naver.com</t>
+          <t>eudemonic005@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -765,22 +765,22 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 불당24로 9 불당LH 1단지, 단지내상가 오늘지나네일</t>
+          <t>충남 천안시 서북구 불당25로 8 나동 131호 이구네일</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_xlxgxois/83330073</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -796,7 +796,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -805,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>6934</v>
+        <v>5832</v>
       </c>
       <c r="Q4" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="R4" t="n">
-        <v>6960</v>
+        <v>5871</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,12 +820,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1817373039</t>
+          <t>1108135278</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1817373039</t>
+          <t>https://m.place.naver.com/place/1108135278</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>이구네일 백석점</t>
+          <t>오늘지나네일</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -855,12 +855,12 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 한들3로 51 1층 101호</t>
+          <t>충남 천안시 서북구 불당24로 9 불당LH 1단지, 단지내상가 오늘지나네일</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/29nailro10</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -891,17 +891,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2340</v>
+        <v>6936</v>
       </c>
       <c r="Q5" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="R5" t="n">
-        <v>2356</v>
+        <v>6962</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -910,12 +910,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1041668384</t>
+          <t>1817373039</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1041668384</t>
+          <t>https://m.place.naver.com/place/1817373039</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1034,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>이엘네일</t>
+          <t>보니타네일 두정점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>elwaxing@naver.com</t>
+          <t>liasec@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1412-2451</t>
+          <t>0507-1392-8228</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 불당31길 26 지혜성빌 101호</t>
+          <t>충남 천안시 서북구 오성로 61 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/ellash_nail</t>
+          <t>https://www.instagram.com/bonitanail_5668228</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1076,14 +1076,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc53pk</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1095,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1137</v>
+        <v>193</v>
       </c>
       <c r="Q7" t="n">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="R7" t="n">
-        <v>1225</v>
+        <v>264</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1713959834</t>
+          <t>1509710579</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1713959834</t>
+          <t>https://m.place.naver.com/place/1509710579</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1132,29 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>네일라비아</t>
+          <t>이엘네일</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sun_jeong2@naver.com</t>
+          <t>elwaxing@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1459-2062</t>
+          <t>0507-1412-2451</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 두정중10길 2 타워오피스텔 1층 네일라비아</t>
+          <t>충남 천안시 서북구 불당31길 26 지혜성빌 101호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_rabia__</t>
+          <t>http://www.instagram.com/ellash_nail</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1179,7 +1175,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w46h39</t>
+          <t>https://talk.naver.com/ct/wc53pk</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1193,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>359</v>
+        <v>1139</v>
       </c>
       <c r="Q8" t="n">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="R8" t="n">
-        <v>385</v>
+        <v>1227</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1208,12 +1204,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1958470967</t>
+          <t>1713959834</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1958470967</t>
+          <t>https://m.place.naver.com/place/1713959834</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1230,29 +1226,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>네일한누리</t>
+          <t>네일라비아</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>princess5648@naver.com</t>
+          <t>sun_jeong2@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1348-7712</t>
+          <t>0507-1459-2062</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>충남 천안시 동남구 서부대로 252 상가동 2층 203호</t>
+          <t>충남 천안시 서북구 두정중10길 2 타워오피스텔 1층 네일라비아</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail._.han_nury?igsh=MTU5aW1kMnFlZTd2dg==</t>
+          <t>https://www.instagram.com/nail_rabia__</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1277,12 +1273,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wzcv22w</t>
+          <t>https://talk.naver.com/ct/w46h39</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1291,13 +1287,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>314</v>
+        <v>359</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="R9" t="n">
-        <v>318</v>
+        <v>385</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1306,12 +1302,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1718734202</t>
+          <t>1958470967</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1718734202</t>
+          <t>https://m.place.naver.com/place/1958470967</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1328,29 +1324,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>네일하우스</t>
+          <t>네일주아</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>toy_21c@naver.com</t>
+          <t>dmsrud1595@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1356-3410</t>
+          <t>0507-1384-1595</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 두정중9길 1-4 1층</t>
+          <t>충남 천안시 서북구 불당25로 176 1층 130호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tjsl_1</t>
+          <t>https://www.instagram.com/nail._jua</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1375,12 +1371,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wlbvzh7</t>
+          <t>https://talk.naver.com/ct/w5vj1h</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1389,13 +1385,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>47</v>
+        <v>185</v>
       </c>
       <c r="Q10" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="R10" t="n">
-        <v>81</v>
+        <v>211</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1404,12 +1400,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1578775754</t>
+          <t>1139364671</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1578775754</t>
+          <t>https://m.place.naver.com/place/1139364671</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1486,10 +1482,10 @@
         <v>73</v>
       </c>
       <c r="Q11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R11" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1618,29 +1614,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>네일레이어</t>
+          <t>멜루네일</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>naillayer-@naver.com</t>
+          <t>ssunii76_@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1362-6230</t>
+          <t>0507-1312-4412</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 두정로 236 스타펠리스218호</t>
+          <t>충남 천안시 서북구 서부11길 50 블루빌 1층 101호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/naillayer-</t>
+          <t>https://www.instagram.com/melu_nail_</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1655,15 +1651,19 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wzwjq2c</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>X</t>
@@ -1675,13 +1675,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="Q13" t="n">
         <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1690,12 +1690,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2044059918</t>
+          <t>2054396755</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2044059918</t>
+          <t>https://m.place.naver.com/place/2054396755</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1712,29 +1712,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>멜루네일</t>
+          <t>네일레이어</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ssunii76_@naver.com</t>
+          <t>naillayer-@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1312-4412</t>
+          <t>0507-1362-6230</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 서부11길 50 블루빌 1층 101호</t>
+          <t>충남 천안시 서북구 두정로 236 스타펠리스218호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/melu_nail_</t>
+          <t>https://blog.naver.com/naillayer-</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1749,19 +1749,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wzwjq2c</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>X</t>
@@ -1773,13 +1769,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="Q14" t="n">
         <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1788,12 +1784,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2054396755</t>
+          <t>2044059918</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2054396755</t>
+          <t>https://m.place.naver.com/place/2044059918</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1810,25 +1806,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>네일이로에</t>
+          <t>브리네일</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>aeunzxn@naver.com</t>
+          <t>jv1110@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1306-1557</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>충남 천안시 동남구 충절로 79 1층</t>
+          <t>충남 천안시 서북구 월봉4로 84-5 D동 101호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_iroe</t>
+          <t>https://www.instagram.com/brie_nail?igsh=YzNnaDB2MGhlaXo5&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1848,13 +1848,17 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wfwafxh</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1863,13 +1867,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1878,12 +1882,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2016538852</t>
+          <t>2047884394</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2016538852</t>
+          <t>https://m.place.naver.com/place/2047884394</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1900,29 +1904,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>브리네일</t>
+          <t>오온뷰티스튜디오</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>jv1110@naver.com</t>
+          <t>naildre1213@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0507-1306-1557</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 월봉4로 84-5 D동 101호</t>
+          <t>충남 천안시 서북구 성성8로 4 센텀빌딩 1층 107호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/brie_nail?igsh=YzNnaDB2MGhlaXo5&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/oon__bt?igsh=dG1vNzdvdW5zbDlt&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wfwafxh</t>
+          <t>https://talk.naver.com/ct/whmxsvn</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1961,13 +1961,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1976,12 +1976,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2047884394</t>
+          <t>2027623958</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2047884394</t>
+          <t>https://m.place.naver.com/place/2027623958</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1998,34 +1998,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>네오뷰티네일</t>
+          <t>네일이로에</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>sum_mer_lov_e@naver.com</t>
+          <t>aeunzxn@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0507-1393-1054</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>충남 천안시 동남구 통정10로 69-7 2층 202호</t>
+          <t>충남 천안시 동남구 충절로 79 1층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/neo_beauty_sunny?igsh=MThkOTR2cHJoczhhNw==</t>
+          <t>https://www.instagram.com/nail_iroe</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2035,7 +2031,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2046,7 +2042,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2055,13 +2051,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2070,12 +2066,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2080241609</t>
+          <t>2016538852</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2080241609</t>
+          <t>https://m.place.naver.com/place/2016538852</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">

--- a/naver-place-crawler/results_nail/천안_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/천안_네일샵.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>es111222@naver.com</t>
+          <t>sgh2924@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://instagram.com/zeze._nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -665,11 +665,7 @@
           <t>이구네일 백석점</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>zpzp9285@naver.com</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
@@ -680,7 +676,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/29nailro10</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +686,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -715,13 +711,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2341</v>
+        <v>2342</v>
       </c>
       <c r="Q3" t="n">
         <v>16</v>
       </c>
       <c r="R3" t="n">
-        <v>2357</v>
+        <v>2358</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -740,7 +736,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -757,7 +753,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>eudemonic005@naver.com</t>
+          <t>29nail@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -770,17 +766,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xlxgxois/83330073</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -830,7 +826,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -895,13 +891,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>6936</v>
+        <v>6940</v>
       </c>
       <c r="Q5" t="n">
         <v>26</v>
       </c>
       <c r="R5" t="n">
-        <v>6962</v>
+        <v>6966</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -920,7 +916,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -997,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3112</v>
+        <v>3115</v>
       </c>
       <c r="Q6" t="n">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="R6" t="n">
-        <v>3701</v>
+        <v>3705</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1022,7 +1018,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1030,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>보니타네일 두정점</t>
+          <t>이엘네일</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>liasec@naver.com</t>
+          <t>elwaxing@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1392-8228</t>
+          <t>0507-1412-2451</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 오성로 61 4층</t>
+          <t>충남 천안시 서북구 불당31길 26 지혜성빌 101호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bonitanail_5668228</t>
+          <t>http://www.instagram.com/ellash_nail</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1076,10 +1072,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc53pk</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>193</v>
+        <v>1142</v>
       </c>
       <c r="Q7" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="R7" t="n">
-        <v>264</v>
+        <v>1230</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1509710579</t>
+          <t>1713959834</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1509710579</t>
+          <t>https://m.place.naver.com/place/1713959834</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1128,29 +1128,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>이엘네일</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>elwaxing@naver.com</t>
-        </is>
-      </c>
+          <t>네일하우스</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1412-2451</t>
+          <t>0507-1356-3410</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 불당31길 26 지혜성빌 101호</t>
+          <t>충남 천안시 서북구 두정중9길 1-4 1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/ellash_nail</t>
+          <t>https://www.instagram.com/tjsl_1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1175,7 +1171,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc53pk</t>
+          <t>https://talk.naver.com/ct/wlbvzh7</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1189,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1139</v>
+        <v>47</v>
       </c>
       <c r="Q8" t="n">
-        <v>88</v>
+        <v>34</v>
       </c>
       <c r="R8" t="n">
-        <v>1227</v>
+        <v>81</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1713959834</t>
+          <t>1578775754</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1713959834</t>
+          <t>https://m.place.naver.com/place/1578775754</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1226,29 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>네일라비아</t>
+          <t>레푸스 천안두정점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sun_jeong2@naver.com</t>
+          <t>refusscheonan@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1459-2062</t>
+          <t>0507-1440-0145</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 두정중10길 2 타워오피스텔 1층 네일라비아</t>
+          <t>충남 천안시 서북구 두정로 177 고바우빌딩 2F</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_rabia__</t>
+          <t>https://blog.naver.com/refusscheonan</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1263,7 +1259,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1273,12 +1269,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w46h39</t>
+          <t>https://talk.naver.com/ct/w5t6e6</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1287,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>359</v>
+        <v>2287</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>550</v>
       </c>
       <c r="R9" t="n">
-        <v>385</v>
+        <v>2837</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1302,17 +1298,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1958470967</t>
+          <t>20103899</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1958470967</t>
+          <t>https://m.place.naver.com/place/20103899</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1324,29 +1320,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>네일주아</t>
+          <t>로즈샵</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dmsrud1595@naver.com</t>
+          <t>rose202301@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1384-1595</t>
+          <t>0507-1398-0934</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 불당25로 176 1층 130호</t>
+          <t>충남 천안시 서북구 오성로 120 로즈샵</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail._jua</t>
+          <t>https://www.instagram.com/rose_nail_shop</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1371,12 +1367,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5vj1h</t>
+          <t>https://talk.naver.com/ct/w4h5hi</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1385,13 +1381,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>185</v>
+        <v>1755</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>452</v>
       </c>
       <c r="R10" t="n">
-        <v>211</v>
+        <v>2207</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1400,17 +1396,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1139364671</t>
+          <t>1160095575</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1139364671</t>
+          <t>https://m.place.naver.com/place/1160095575</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1436,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nail_leehyeon</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1450,12 +1446,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1479,13 +1475,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q11" t="n">
         <v>22</v>
       </c>
       <c r="R11" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1504,7 +1500,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1538,17 +1534,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_wKKgn</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1602,7 +1598,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1632,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/melu_nail_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1646,7 +1642,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1675,13 +1671,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Q13" t="n">
         <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1700,7 +1696,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1730,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/naillayer-</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1744,12 +1740,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1794,289 +1790,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>브리네일</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>jv1110@naver.com</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0507-1306-1557</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>충남 천안시 서북구 월봉4로 84-5 D동 101호</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/brie_nail?igsh=YzNnaDB2MGhlaXo5&amp;utm_source=qr</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wfwafxh</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>19</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>2047884394</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2047884394</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>오온뷰티스튜디오</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>naildre1213@naver.com</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>충남 천안시 서북구 성성8로 4 센텀빌딩 1층 107호</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/oon__bt?igsh=dG1vNzdvdW5zbDlt&amp;utm_source=qr</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/whmxsvn</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3</v>
-      </c>
-      <c r="R16" t="n">
-        <v>10</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>2027623958</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2027623958</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>네일아트,네일샵</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>네일이로에</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>aeunzxn@naver.com</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>충남 천안시 동남구 충절로 79 1층</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/nail_iroe</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3</v>
-      </c>
-      <c r="R17" t="n">
-        <v>49</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>2016538852</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2016538852</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
